--- a/Testing/native-subscription-postgres-test-cases.xlsx
+++ b/Testing/native-subscription-postgres-test-cases.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo setup" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test cases'!$A$1:$H$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Demo cases'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test cases'!$A$1:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Demo cases'!$A$1:$F$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -502,189 +502,185 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Where</t>
+          <t>Connection mode</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Local ARAK against a local PostgreSQL 16 container (database salesdb, schemas demo_lookup and sales). Every case ran against the real database: psql as each demo login confirms what PostgreSQL itself allows.</t>
+          <t>One connection has one enforcement mode, for subscription and data policies alike. ARAK pushes roles only to a connection set to Native source config; on any other mode plans are refused, Check says nobody should hold a left-over role, and the sweep empties it. The mode cannot move off Native while a role is pushed. Queries through ARAK work on every mode, and the proxy answers exactly as before (NM-09, NM-12).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>When</t>
+          <t>Where</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>Local ARAK against a local PostgreSQL 16 container (database salesdb, schemas demo_lookup and sales), demo-pg set to Native source config. Every case ran against the real database: psql as each demo login confirms what PostgreSQL itself allows. All cases were run again, from a clean start, on the final build of the connection-mode change.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Passwords</t>
+          <t>When</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>None in this file. Demo logins use &lt;demo password&gt;; the push account is stored by ARAK as a sealed reference and never returned.</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Passwords</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>None in this file. Demo logins use &lt;demo password&gt;; the push account is stored by ARAK as a sealed reference and never returned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Sheets</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Test cases: every case with steps, expected and actual result. Demo cases: a script for showing the feature, each pointing at its test cases. Demo setup: people, logins, policies and accounts the cases use.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Push account</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Logins</t>
+          <t>Push account</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Plan and apply (Read)</t>
+          <t>Logins</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Review and staleness</t>
+          <t>Plan and apply (Read)</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Review and staleness</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Browse</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Levels</t>
+          <t>Browse</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Fail closed</t>
+          <t>Levels</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -700,97 +696,145 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>Fail closed</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Other readers</t>
+          <t>Refused</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Sweep</t>
+          <t>Other readers</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Rollback</t>
+          <t>Sweep</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Rollback</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Connection mode</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Proxy unchanged</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="C23" s="6" t="n">
+      <c r="B26" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="C26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="6" t="n">
-        <v>60</v>
+      <c r="D26" s="6" t="n">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -804,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -897,7 +941,7 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -939,7 +983,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -981,7 +1025,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1067,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1089,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>As native_author (POLICY_AUTHOR, password already changed) PUT the push account</t>
+          <t>As native_author (POLICY_AUTHOR) PUT the push account</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1065,7 +1109,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1151,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1193,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1235,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1277,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1319,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1361,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1403,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1445,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1477,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>['nat_team is shared by native_fay (who qualify) and native_gus (who do not), so it stays out of the role.']</t>
+          <t>['nat_team is shared by native_fay (who qualifies) and native_gus (who does not), so it stays out of the role.']</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -1443,7 +1487,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1529,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1571,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1613,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1655,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1697,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1739,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1781,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1823,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1865,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1907,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1949,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1991,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1990,7 +2034,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2066,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>plan warning=['arak_sub_17077928_18de535d holds SELECT on demo_lookup.division_value granted by postgres; ARAK does not revoke it.']; check(200) warning=['arak_sub_17077928_18de535d holds SELECT on demo_lookup.division_value granted by postgres; ARAK does not revoke it.']; after DBA revoke nat_ann=denied</t>
+          <t>plan warning=['arak_sub_17077928_18de535d holds SELECT on demo_lookup.division_value granted by postgres; ARAK does not revoke it.']; check(200) warning=['arak_sub_17077928_18de535d holds SELECT on demo_lookup.division_value granted by postgres; ARAK does not revoke it.']; plan steps=[]; after DBA revoke nat_ann=denied</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -2032,7 +2076,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2118,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2160,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2202,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2244,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2286,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2328,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2370,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2412,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2454,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2496,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2538,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2580,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2622,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2664,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2706,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2748,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2790,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2832,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2874,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2916,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2958,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2956,7 +3000,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -2998,7 +3042,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3084,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3126,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3168,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3210,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3252,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3284,7 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>delete 200; plan 422: No push account is set for demo-pg. A platform admin sets one under PostgreSQL roles, Source setup: an account with CREATEROLE and grant options ...; check 422; set again 200; plan 200 changes=[]; secretless=True</t>
+          <t>delete 200; plan 422: No push account is set for demo-pg. A platform admin sets one under PostgreSQL roles, Source setup: an account; check 422; members kept=nat_ann,nat_ben,nat_cat; set again 200; plan 200 changes=[]; secretless=True</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -3250,7 +3294,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3326,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>source entries=20 e.g. 'Push account set (fernet)', 'Push account removed. Roles already applied stay on the sour...'; policy actions=[('APPLY', 'APPLIED'), ('APPLY', 'STALE'), ('DRIFT_CHECK', 'DRIFTED'), ('DRIFT_CHECK', 'IN_SYNC'), ('DRIFT_CHECK', 'PENDING'), ('DRIFT_CHECK', 'REFUSED'), ('DRY_RUN', 'REFUSED'), ('DRY_RUN', 'REVIEWED'), ('EXPIRE', 'APPLIED'), ('ROLLBACK', 'ROLLED_BACK')]; actors=['admin', 'native_author', 'system:native-sweep']; secretless=True; client address fields=False</t>
+          <t>source entries=44 e.g. 'Push account set (fernet)', 'Push account removed. Roles already applied stay on the sour...'; policy actions=[('APPLY', 'APPLIED'), ('APPLY', 'REFUSED'), ('APPLY', 'STALE'), ('DRIFT_CHECK', 'DRIFTED'), ('DRIFT_CHECK', 'IN_SYNC'), ('DRIFT_CHECK', 'PENDING'), ('DRIFT_CHECK', 'REFUSED'), ('DRY_RUN', 'REFUSED'), ('DRY_RUN', 'REVIEWED'), ('EXPIRE', 'APPLIED'), ('ROLLBACK', 'ROLLED_BACK')]; actors=['admin', 'native_author', 'system:native-sweep']; secretless=True; client address fields=False</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
@@ -3292,7 +3336,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3368,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Sweep log: 2 role(s) checked, 1 revoked from. Role arak_sub_&lt;policy&gt;_&lt;source&gt; has no nat_ member; still NOLOGIN with CONNECT and USAGE. nat_ann has no USAGE on sales. History: EXPIRE APPLIED by system:native-sweep, 'Taken away because the policy no longer gives it: revoke member nat_ann, revoke member nat_cat'.</t>
+          <t>role members=''; role login|CONNECT|USAGE=f|t|t; nat_ann USAGE on sales=f; history: system:native-sweep EXPIRE APPLIED 'Taken away because the policy no longer gives it: revoke member nat_ann, revoke member nat_cat'</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -3334,7 +3378,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3410,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Plan: 4 GRANT_MEMBER steps (nat_ann, nat_ben, nat_cat, nat_dan; WITH INHERIT TRUE, SET FALSE). Apply 200. Check APPLIED with no changes. Members nat_ann, nat_ben, nat_cat, nat_dan. nat_dan: USAGE on sales true, SELECT on sales.customer false. native-demo-read-table still APPLIED.</t>
+          <t>activate 200 ACTIVE; members right after=''; plan steps=[('GRANT_MEMBER', 'nat_ann'), ('GRANT_MEMBER', 'nat_ben'), ('GRANT_MEMBER', 'nat_cat'), ('GRANT_MEMBER', 'nat_dan')]; apply 200; check=APPLIED; members=nat_ann,nat_ben,nat_cat,nat_dan; nat_dan USAGE|SELECT=t|f; read-table check=PENDING</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
@@ -3376,12 +3420,516 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>2026-10-03 / 2026-10-04</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>NM-01</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Connection mode</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Plan is refused on a connection set to the query proxy</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade case: on the PR #16 build demo-pg was moved to Query proxy while both roles were pushed. Start this build. As admin, Plan native-demo-read-table</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>422. The message names the mode (query proxy) and says to set native source config under Sources. Nothing is planned; the refusal is audited</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>422: demo-pg is enforced by the query proxy, not native source config, so its policies are not pushed to it as roles. Set it to native source config under Sources to push them. Audit: DRY_RUN REFUSED by admin</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>NM-02</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Connection mode</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Check of a role left under the proxy says nobody should hold it</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Same state. Check native-demo-read-table, then list the role's members in PostgreSQL</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>200. Status PENDING, not satisfied. A warning names the mode and ends 'Nobody should hold the role: roll it back.' Only revoke steps are listed. The check changes nothing at the source</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>200, status PENDING, satisfied False. Warning: demo-pg is enforced by the query proxy, not native source config, so its policies are not pushed to it as roles. Set it to native source config under Sources to push them. Nobody should hold the role: roll it back. Changes: COMMENT_ROLE, REVOKE_MEMBER, REVOKE_MEMBER, REVOKE_MEMBER, REVOKE_SELECT, REVOKE_USAGE. Members before 'nat_ann,nat_ben,nat_cat', after 'nat_ann,nat_ben,nat_cat'</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>NM-03</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Connection mode</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>The sweep empties roles left under another mode</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Same start as NM-01 (both roles hold members under Query proxy). Wait for the first sweep (60 s after start). List members and table grants</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Log line 'Native sweep: 2 role(s) checked, 2 revoked from'. Every member and every table grant is taken away; the roles stay, so they can be rolled back. Two EXPIRE audits by system:native-sweep: 'Taken away because nobody should hold the role: ...' with the mode in brackets</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Log: 'Native sweep: 2 role(s) checked, 2 revoked from, 0 drifted, 0 pending, 0 failed'. Members read-table '', browse ''; table grants 0. Audits: system:native-sweep EXPIRE APPLIED 'Taken away because nobody should hold the role: revoke member nat_ann, revoke member nat_ben, revoke member nat_cat, revoke select demo_lookup.department_division, revoke...'; browse: system:native-sweep EXPIRE</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>NM-04</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Connection mode</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>The mode cannot move off native while roles are installed</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>With both roles installed, save demo-pg with mode Secure view (from Query proxy)</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>409: roll the roles back first, under each policy's PostgreSQL roles tab. The mode stays Query proxy</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>409: demo-pg has subscription policies pushed to it as PostgreSQL roles. Roll them back first, under each policy's PostgreSQL roles tab, then change its enforcement mode. Mode afterwards: PROXY</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>NM-05</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Connection mode</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Saving a connection with the same mode still works</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Same state. Save demo-pg again with mode Query proxy (unchanged)</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>200; the lock only stops a change of mode</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>200: mode PROXY</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>NM-06</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Connection mode</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Rollback works under any mode</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Under Query proxy, ask for the rollback plan of native-demo-read-table</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>200 with the script that revokes ARAK's grants and drops the role</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>200: steps ['REVOKE_MEMBER', 'REVOKE_MEMBER', 'REVOKE_MEMBER', 'REVOKE_SELECT', 'REVOKE_USAGE', 'REVOKE_CONNECT', 'DROP_ROLE']</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>NM-07</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Connection mode</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Switching to native is always allowed</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Roles still installed (empty). Save demo-pg with mode Native source config</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>200; mode NATIVE_CONFIG</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>200: mode NATIVE_CONFIG</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>NM-08</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Connection mode</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Moving back off native is refused while roles are installed</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Now on Native source config with the roles installed, save demo-pg with mode Query proxy</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>409 with the roll-back-first message; the mode stays NATIVE_CONFIG</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>409: demo-pg has subscription policies pushed to it as PostgreSQL roles. Roll them back first, under each policy's PostgreSQL roles tab, then change its enforcement mode. Mode afterwards: NATIVE_CONFIG</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>NM-09</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Proxy unchanged</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>The query proxy answers exactly as before (old build on proxy vs new build on native)</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>On the PR #16 build, with demo-pg on Query proxy, run 10 statements through /v1/query as each of the 41 enabled local users (admin runs them as each user): five tables, a join, a CTE, a DELETE, a pg_roles read, a table-free SELECT. Take it twice. Then on this build, with demo-pg on Native source config, take it again. Compare status, columns, rows, rewritten SQL and explanations.</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>Both PR #16 runs match each other, and this build matches them, query for query.</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>410 queries per run, 58 answered 200 with 98 rows in all, the rest refused as before (denies, DELETE refused, unqualified pg_roles refused). old1 vs old2: 0 differ. old1 vs the final build on native, roles applied: 0 differ.</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>NM-10</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Connection mode</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>With nothing pushed, a source can leave native source config</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Roll back both demo roles. As admin set demo-pg to the query proxy and save; plan native-demo-read-table</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>Save 200 (no role is installed, so nothing blocks the change); the plan is refused with 422 because demo-pg is now enforced by the query proxy</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>save 200 mode=PROXY; plan 422: demo-pg is enforced by the query proxy, not native source config, so its policies are not pushed to it as roles. Set it to native source config under Sources to</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>NM-11</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Connection mode</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>A plan made under native source config is not applied after the source moved to the proxy</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Set demo-pg to native source config; plan native-demo-read-table; set demo-pg to the query proxy (allowed, nothing is installed); apply the plan; set demo-pg back to native source config</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Apply 422 with the mode message; nothing is created on PostgreSQL; the policy history has APPLY REFUSED with the same message</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>native 200; plan 200; proxy 200; apply 422: demo-pg is enforced by the query proxy, not native source config, so its policies are not pushed to it as roles. Set it to native source con; role exists=False; history=APPLY REFUSED; back to native 200</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>NM-12</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Proxy unchanged</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>The query proxy answers exactly as before on the final build, on either mode</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>On the final build of this change: with nothing pushed and demo-pg on Query proxy, run the NM-09 statements (41 enabled local users x 10 statements). At the end of all cases, with both roles applied and demo-pg on Native source config, run them again. Compare each with the PR #16 run</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Both runs match the PR #16 run query for query: the connection mode and the roles on the source do not change what the proxy answers</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>410 queries, 58 answered 200 with 98 rows. old1 vs newproxy1 : 410 vs 410 queries, 0 differ; old1 vs newnative2 : 410 vs 410 queries, 0 differ</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H61"/>
+  <autoFilter ref="A1:H73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3392,7 +3940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3438,389 +3986,421 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>D-00</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Set up the source</t>
+          <t>One connection, one mode</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>ARAK pushes with its own account, never the proxy's read-only one.</t>
+          <t>A connection's enforcement mode decides for every policy on it: subscription and data policies alike.</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Any subscription policy &gt; PostgreSQL roles &gt; Source setup &gt; Push account. Try the proxy's login: refused. Give arak_push (CREATEROLE, grant options) with &lt;demo password&gt;. Show that the page only says 'Set (fernet) ... It is never shown again.' and never shows the login or password back.</t>
+          <t>Sources &gt; demo-pg &gt; Enforcement mode. With demo-pg on Query proxy, open native-demo-read-table &gt; PostgreSQL roles: the tab says the policy is enforced by the query proxy and offers nothing to push. Set demo-pg to Native source config; the tab now plans and applies. While a role is pushed, try to set the mode back: refused until the roles are rolled back.</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Refusal names the reason; the saved account is a sealed reference; Setup history has the change.</t>
+          <t>Push only on a native connection; the mode cannot change under pushed roles; queries through ARAK keep working on either mode.</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>NS-01, NS-03, NS-04, NS-06</t>
+          <t>NM-01 to NM-12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Map people to the logins they already have</t>
+          <t>Set up the source</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>ARAK never creates logins; it uses the ones the DBA made.</t>
+          <t>ARAK pushes with its own account, never the proxy's read-only one.</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Source setup &gt; Database logins: map native_ann to nat_ann ... native_fay and native_gus both to nat_team. Try to map yourself: refused.</t>
+          <t>Any subscription policy &gt; PostgreSQL roles &gt; Source setup &gt; Push account. Try the proxy's login: refused. Give arak_push (CREATEROLE, grant options) with &lt;demo password&gt;. Show that the page only says 'Set (fernet) ... It is never shown again.' and never shows the login or password back.</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Mappings listed per person; no self-mapping; Setup history shows each change.</t>
+          <t>Refusal names the reason; the saved account is a sealed reference; Setup history has the change.</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>NS-07, NS-08, NS-10</t>
+          <t>NS-01, NS-03, NS-04, NS-06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Plan at Read: who is in, who is out, and why</t>
+          <t>Map people to the logins they already have</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>The plan explains every person the policy decides about before anything runs.</t>
+          <t>ARAK never creates logins; it uses the ones the DBA made.</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Open native-demo-read-table &gt; PostgreSQL roles &gt; Level Read &gt; Plan (as native_author is fine).</t>
+          <t>Source setup &gt; Database logins: map native_ann to nat_ann ... native_fay and native_gus both to nat_team. Try to map yourself: refused.</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Members nat_ann, nat_ben, nat_cat. Dan exempt (until his exemption ends). Eve has no login. nat_team left out because Fay qualifies and Gus does not. PUBLIC CONNECT warning. The SQL that would run and the rollback script.</t>
+          <t>Mappings listed per person; no self-mapping; Setup history shows each change.</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NS-11 to NS-15</t>
+          <t>NS-07, NS-08, NS-10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Apply and prove it in PostgreSQL</t>
+          <t>Plan at Read: who is in, who is out, and why</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Only a platform admin applies, and only the plan that was reviewed.</t>
+          <t>The plan explains every person the policy decides about before anything runs.</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>As native_author the plan has no Apply button ('Only a platform administrator can apply a plan.'; the API refuses with 403). As admin: Apply this plan. In psql as nat_ann SELECT demo_lookup.department_division (works) and demo_lookup.division_value (refused); as nat_out (refused).</t>
+          <t>Open native-demo-read-table &gt; PostgreSQL roles &gt; Level Read &gt; Plan (as native_author is fine).</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Role arak_sub_&lt;policy&gt;_&lt;source&gt; created NOLOGIN with ARAK's comment; members inherit, cannot SET ROLE.</t>
+          <t>Members nat_ann, nat_ben, nat_cat. Dan exempt (until his exemption ends). Eve has no login. nat_team left out because Fay qualifies and Gus does not. PUBLIC CONNECT warning. The SQL that would run and the rollback script.</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>NS-16 to NS-21</t>
+          <t>NS-11 to NS-15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Browse versus Read</t>
+          <t>Apply and prove it in PostgreSQL</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Browse lets people find the schema; Read lets them SELECT.</t>
+          <t>Only a platform admin applies, and only the plan that was reviewed.</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>native-demo-browse-sales: plan at Browse and apply. As nat_ann: USAGE on sales yes, SELECT on sales.customer refused. Compare information_schema.tables with pg_tables. Then switch native-demo-read-table to Browse and back to Read.</t>
+          <t>As native_author the plan has no Apply button ('Only a platform administrator can apply a plan.'; the API refuses with 403). As admin: Apply this plan. In psql as nat_ann SELECT demo_lookup.department_division (works) and demo_lookup.division_value (refused); as nat_out (refused).</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Browse = CONNECT + USAGE only. information_schema hides tables without a privilege; pg_catalog shows every name (the plan warns). Switching level plans only REVOKE_SELECT or GRANT_SELECT.</t>
+          <t>Role arak_sub_&lt;policy&gt;_&lt;source&gt; created NOLOGIN with ARAK's comment; members inherit, cannot SET ROLE.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NS-34 to NS-38</t>
+          <t>NS-16 to NS-21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Fail closed when part of the role is refused</t>
+          <t>Browse versus Read</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>A role is all or nothing, so anyone refused one table is kept out of the whole role.</t>
+          <t>Browse lets people find the schema; Read lets them SELECT.</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Plan native-demo-read-lookup (two tables) at Read.</t>
+          <t>native-demo-browse-sales: plan at Browse and apply. As nat_ann: USAGE on sales yes, SELECT on sales.customer refused. Compare information_schema.tables with pg_tables. Then switch native-demo-read-table to Browse and back to Read.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Cat: 'denied by native-demo-deny-one-table', loses department_division too. Others: 'not let in by &lt;the policy holding the gate&gt;'. Lost tables are listed. Nothing is applied.</t>
+          <t>Browse = CONNECT + USAGE only. information_schema hides tables without a privilege; pg_catalog shows every name (the plan warns). Switching level plans only REVOKE_SELECT or GRANT_SELECT.</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>NS-39, NS-40</t>
+          <t>NS-34 to NS-38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>What cannot be pushed</t>
+          <t>Fail closed when part of the role is refused</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conditions PostgreSQL cannot check at connect time are refused, not half-enforced.</t>
+          <t>A role is all or nothing, so anyone refused one table is kept out of the whole role.</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Plan each of native-demo-refused-time, -network, -purpose, -context, -no-table, the DENY policy, a data policy and native-demo-draft.</t>
+          <t>Plan native-demo-read-lookup (two tables) at Read.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>422 with the reason and 'use the query proxy'; the draft plans with no members and says why.</t>
+          <t>Cat: 'denied by native-demo-deny-one-table', loses department_division too. Others: 'not let in by &lt;the policy holding the gate&gt;'. Lost tables are listed. Nothing is applied.</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NS-41 to NS-48</t>
+          <t>NS-39, NS-40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Hand changes: drift, repair, and what ARAK leaves alone</t>
+          <t>What cannot be pushed</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>ARAK owns only what its account granted.</t>
+          <t>Conditions PostgreSQL cannot check at connect time are refused, not half-enforced.</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>As DBA grant SELECT on division_value to the role: plan and Check warn 'granted by postgres; ARAK does not revoke it'. Same grant made as arak_push: Check says DRIFTED with REVOKE_SELECT; plan and apply repair it. Revoke a member by hand: Check shows GRANT_MEMBER; apply puts it back.</t>
+          <t>Plan each of native-demo-refused-time, -network, -purpose, -context, -no-table, the DENY policy, a data policy and native-demo-draft.</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Foreign grants reported, never revoked; ARAK's own drift found and repaired.</t>
+          <t>422 with the reason and 'use the query proxy'; the draft plans with no members and says why.</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>NS-28 to NS-31, NS-33</t>
+          <t>NS-41 to NS-48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>D-09</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>A reviewed plan is used once and only while it is true</t>
+          <t>Hand changes: drift, repair, and what ARAK leaves alone</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Apply runs exactly what was reviewed, or nothing.</t>
+          <t>ARAK owns only what its account granted.</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Apply a review twice; apply it to another policy; change a mapping between plan and apply.</t>
+          <t>As DBA grant SELECT on division_value to the role: plan and Check warn 'granted by postgres; ARAK does not revoke it'. Same grant made as arak_push: Check says DRIFTED with REVOKE_SELECT; plan and apply repair it. Revoke a member by hand: Check shows GRANT_MEMBER; apply puts it back.</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Used-once, wrong-policy and stale plans are refused (409); a fresh plan shows the difference.</t>
+          <t>Foreign grants reported, never revoked; ARAK's own drift found and repaired.</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NS-22 to NS-27, NS-29, NS-32</t>
+          <t>NS-28 to NS-31, NS-33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-09</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>The sweep (every 10 minutes) only takes away</t>
+          <t>A reviewed plan is used once and only while it is true</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>A role does not ask ARAK anything, so the sweep is what ends access on the source.</t>
+          <t>Apply runs exactly what was reviewed, or nothing.</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Remove native_ben from the group, unmap native_dan, add native_out; wait for the sweep. Disable native-demo-browse-sales; wait again; activate it, plan and apply.</t>
+          <t>Apply a review twice; apply it to another policy; change a mapping between plan and apply.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Ben and Dan revoked (EXPIRE by system:native-sweep); Out not added (role PENDING until a person plans); the disabled policy's role is emptied.</t>
+          <t>Used-once, wrong-policy and stale plans are refused (409); a fresh plan shows the difference.</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>NS-50 to NS-52, NS-59, NS-60</t>
+          <t>NS-22 to NS-27, NS-29, NS-32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Rollback</t>
+          <t>The sweep (every 10 minutes) only takes away</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Undo is planned and reviewed like an apply.</t>
+          <t>A role does not ask ARAK anything, so the sweep is what ends access on the source.</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>As admin: Roll back shows the script under 'Will run'; press 'Drop the role'. A policy author has no Roll back button (through the API they can read the rollback plan; running it is refused). Plan and apply again.</t>
+          <t>Remove native_ben from the group, unmap native_dan, add native_out; wait for the sweep. Disable native-demo-browse-sales; wait again; activate it, plan and apply.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>ARAK's grants revoked then the role dropped; nat_ann refused; re-apply recreates it.</t>
+          <t>Ben and Dan revoked (EXPIRE by system:native-sweep); Out not added (role PENDING until a person plans); the disabled policy's role is emptied.</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NS-53 to NS-56</t>
+          <t>NS-50 to NS-52, NS-59, NS-60</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Rollback</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Undo is planned and reviewed like an apply.</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>As admin: Roll back shows the script under 'Will run'; press 'Drop the role'. A policy author has no Roll back button (through the API they can read the rollback plan; running it is refused). Plan and apply again.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>ARAK's grants revoked then the role dropped; nat_ann refused; re-apply recreates it.</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>NS-53 to NS-56</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
           <t>D-12</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Audit, and no secrets anywhere</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Every step is on the history; no password or client address is ever returned.</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Show Setup history and the policy's History. Remove the push account: Plan and Check are refused and the role on the source stays. Set it again: the plan has nothing to do.</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>CONFIGURE, DRY_RUN, APPLY, DRIFT_CHECK, EXPIRE, ROLLBACK entries with who and why.</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>NS-57, NS-58</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3831,7 +4411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3844,80 +4424,43 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>Source: demo-pg (PostgreSQL, database salesdb). Set its enforcement mode to Native source config under Sources before the demo; on any other mode nothing is pushed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>People in ARAK (group native-demo-readers holds the readers)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ARAK person</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Role in the demo</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>PostgreSQL login</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Why it is there</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>native_ann</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Reader</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>nat_ann</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>Member of every applied role</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>native_ben</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Reader</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>nat_ben</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Member; used for the sweep and membership drift cases</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>native_cat</t>
+          <t>native_ann</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -3927,19 +4470,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>nat_cat</t>
+          <t>nat_ann</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Denied demo_lookup.division_value by native-demo-deny-one-table</t>
+          <t>Member of every applied role</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>native_dan</t>
+          <t>native_ben</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -3949,19 +4492,19 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>nat_dan</t>
+          <t>nat_ben</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Exempt from the Read policies for 30 days</t>
+          <t>Member; used for the sweep and membership drift cases</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>native_eve</t>
+          <t>native_cat</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -3971,19 +4514,19 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>nat_cat</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Qualifies but has no login mapped</t>
+          <t>Denied demo_lookup.division_value by native-demo-deny-one-table</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>native_fay</t>
+          <t>native_dan</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -3993,173 +4536,163 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>nat_team</t>
+          <t>nat_dan</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Shares nat_team with Gus</t>
+          <t>Exempt from the Read policies for 30 days</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>native_gus</t>
+          <t>native_eve</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Not a reader</t>
+          <t>Reader</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>nat_team</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Shares nat_team with Fay, so nat_team stays out</t>
+          <t>Qualifies but has no login mapped</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>native_out</t>
+          <t>native_fay</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Not a reader</t>
+          <t>Reader</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>nat_out</t>
+          <t>nat_team</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Outsider; must always be refused</t>
+          <t>Shares nat_team with Gus</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
+          <t>native_gus</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Not a reader</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>nat_team</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Shares nat_team with Fay, so nat_team stays out</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>native_out</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Not a reader</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>nat_out</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Outsider; must always be refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
           <t>native_author</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Policy author</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Can plan and check; cannot apply, roll back or set accounts</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Policies (all SUBSCRIPTION, environment prod, subject group native-demo-readers unless noted)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Policy</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Effect</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Used as</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>native-demo-read-table</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>TABLE demo_lookup.department_division</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>ALLOW</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Applied at Read</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>native-demo-read-lookup</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>SCHEMA demo_lookup</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>ALLOW</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Planned only: fails closed</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>native-demo-deny-one-table</t>
+          <t>native-demo-read-table</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4169,24 +4702,24 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>TABLE demo_lookup.division_value</t>
+          <t>TABLE demo_lookup.department_division</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>DENY (Cat)</t>
+          <t>ALLOW</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>No role of its own</t>
+          <t>Applied at Read</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>native-demo-browse-sales</t>
+          <t>native-demo-read-lookup</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4196,78 +4729,78 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>SCHEMA sales</t>
+          <t>SCHEMA demo_lookup</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>ALLOW, ends in 90 days</t>
+          <t>ALLOW</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Applied at Browse</t>
+          <t>Planned only: fails closed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>native-demo-refused-time</t>
+          <t>native-demo-deny-one-table</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>SCHEMA demo_lookup</t>
+          <t>TABLE demo_lookup.division_value</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>ALLOW + time window</t>
+          <t>DENY (Cat)</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>No role of its own</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>native-demo-refused-network</t>
+          <t>native-demo-browse-sales</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>SCHEMA demo_lookup</t>
+          <t>SCHEMA sales</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>ALLOW + network range</t>
+          <t>ALLOW, ends in 90 days</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>Applied at Browse</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>native-demo-refused-purpose</t>
+          <t>native-demo-refused-time</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -4282,7 +4815,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>ALLOW + purpose</t>
+          <t>ALLOW + time window</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -4294,7 +4827,7 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>native-demo-refused-context</t>
+          <t>native-demo-refused-network</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4309,7 +4842,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>ALLOW + context expression</t>
+          <t>ALLOW + network range</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -4321,7 +4854,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>native-demo-refused-no-table</t>
+          <t>native-demo-refused-purpose</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4331,125 +4864,141 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>SCHEMA no_such_schema</t>
+          <t>SCHEMA demo_lookup</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>ALLOW</t>
+          <t>ALLOW + purpose</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Refused: binds no table</t>
+          <t>Refused</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
+          <t>native-demo-refused-context</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>SCHEMA demo_lookup</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>ALLOW + context expression</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>native-demo-refused-no-table</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>SCHEMA no_such_schema</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>ALLOW</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Refused: binds no table</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t>native-demo-draft</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>SCHEMA demo_lookup</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>ALLOW</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Plans with no members</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>PostgreSQL accounts on the demo source (passwords: &lt;demo password&gt;, never written down here)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Holds</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>arak_push</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>ARAK's push account</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>CREATEROLE; SELECT WITH GRANT OPTION on the demo tables; not superuser</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>arak_weak</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Push account without CREATEROLE</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Used to show the blocker</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>arak_reader</t>
+          <t>arak_push</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>The query proxy's read-only login</t>
+          <t>ARAK's push account</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Refused as a push account</t>
+          <t>CREATEROLE; SELECT WITH GRANT OPTION on the demo tables; not superuser</t>
         </is>
       </c>
       <c r="D30" s="8" t="n"/>
@@ -4458,17 +5007,17 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>nat_ann ... nat_out, nat_team</t>
+          <t>arak_weak</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>People's existing logins</t>
+          <t>Push account without CREATEROLE</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>LOGIN, no privileges of their own</t>
+          <t>Used to show the blocker</t>
         </is>
       </c>
       <c r="D31" s="8" t="n"/>
@@ -4477,21 +5026,59 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>arak_reader</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>DBA</t>
+          <t>The query proxy's read-only login</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Makes the 'somebody else' grants in the drift cases</t>
+          <t>Refused as a push account</t>
         </is>
       </c>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>nat_ann ... nat_out, nat_team</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>People's existing logins</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>LOGIN, no privileges of their own</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Makes the 'somebody else' grants in the drift cases</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
